--- a/Resources/ExtractFeatures_CL.xlsx
+++ b/Resources/ExtractFeatures_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="-180" windowWidth="15600" windowHeight="13635"/>
+    <workbookView xWindow="1650" yWindow="30" windowWidth="15600" windowHeight="13365"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="2" r:id="rId1"/>
@@ -1757,7 +1757,7 @@
         <v>117</v>
       </c>
       <c r="C1" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>101</v>

--- a/Resources/ExtractFeatures_CL.xlsx
+++ b/Resources/ExtractFeatures_CL.xlsx
@@ -1757,7 +1757,7 @@
         <v>117</v>
       </c>
       <c r="C1" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>101</v>
